--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261021.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261021.xlsx
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>43,783</t>
+          <t>25,881</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,881</t>
+          <t>43,783</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
